--- a/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:57:50+00:00</t>
+    <t>2026-09-17T15:33:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4111" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T15:33:46+00:00</t>
+    <t>2026-09-28T13:37:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1392,159 +1392,9 @@
     <t>Professionnel de santé / Non Professionnel de santé</t>
   </si>
   <si>
-    <t>PractitionerRole.code:classCode.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.system</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.version</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.code</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J141-RoleClass-CISIS/FHIR/JDV-J141-RoleClass-CISIS|20210326120000</t>
   </si>
   <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.display</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.coding.userSelected</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:classCode.text</t>
-  </si>
-  <si>
     <t>PractitionerRole.code:typeCode</t>
   </si>
   <si>
@@ -1554,19 +1404,7 @@
     <t>Type de participation</t>
   </si>
   <si>
-    <t>PractitionerRole.code:typeCode.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:typeCode.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:typeCode.coding</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J144-ParticipationType-CISIS/FHIR/JDV-J144-ParticipationType-CISIS|20210326120000</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:typeCode.text</t>
   </si>
   <si>
     <t>PractitionerRole.specialty</t>
@@ -2304,7 +2142,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO110"/>
+  <dimension ref="A1:AO95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.48046875" customWidth="true" bestFit="true"/>
@@ -9928,11 +9766,11 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>378</v>
+        <v>445</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9982,12 +9820,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
@@ -10005,19 +9845,23 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>105</v>
+        <v>448</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -10041,13 +9885,11 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10065,31 +9907,31 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>78</v>
+        <v>340</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10097,14 +9939,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10120,20 +9962,18 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>112</v>
+        <v>451</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10158,31 +9998,29 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>78</v>
+        <v>453</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>118</v>
+        <v>450</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10194,30 +10032,30 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>78</v>
+        <v>454</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>108</v>
+        <v>455</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>457</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10231,7 +10069,7 @@
         <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>78</v>
@@ -10240,20 +10078,16 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>458</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>425</v>
+        <v>459</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -10301,7 +10135,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10319,24 +10153,24 @@
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10347,10 +10181,10 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -10359,13 +10193,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>104</v>
+        <v>465</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>106</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10416,28 +10250,28 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>107</v>
+        <v>464</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>78</v>
+        <v>468</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>108</v>
+        <v>469</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10448,14 +10282,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>451</v>
+        <v>470</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10465,7 +10299,7 @@
         <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>78</v>
@@ -10474,18 +10308,18 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>111</v>
+        <v>471</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>112</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10521,11 +10355,9 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>116</v>
-      </c>
+        <v>475</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10533,7 +10365,7 @@
         <v>117</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10542,22 +10374,22 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>119</v>
+        <v>476</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>78</v>
+        <v>477</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>108</v>
+        <v>479</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10565,10 +10397,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>453</v>
+        <v>481</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10588,23 +10420,19 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>454</v>
+        <v>105</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10652,7 +10480,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10664,16 +10492,16 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>460</v>
+        <v>108</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10684,21 +10512,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10707,19 +10535,19 @@
         <v>78</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>463</v>
+        <v>112</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>464</v>
+        <v>113</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>465</v>
+        <v>114</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10757,40 +10585,40 @@
         <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>118</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>468</v>
+        <v>108</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10801,12 +10629,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10824,21 +10654,19 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>176</v>
+        <v>485</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>472</v>
+        <v>487</v>
       </c>
       <c r="N73" s="2"/>
-      <c r="O73" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10862,11 +10690,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10884,28 +10714,28 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>118</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10916,10 +10746,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10927,7 +10757,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10942,18 +10772,16 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="N74" s="2"/>
-      <c r="O74" t="s" s="2">
-        <v>482</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10977,13 +10805,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -11001,7 +10829,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -11010,22 +10838,22 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11033,10 +10861,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11044,7 +10872,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>90</v>
@@ -11059,19 +10887,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11120,7 +10948,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11135,16 +10963,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11152,10 +10980,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>434</v>
+        <v>508</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11172,25 +11000,25 @@
         <v>78</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>435</v>
+        <v>509</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>436</v>
+        <v>510</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>437</v>
+        <v>511</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>438</v>
+        <v>512</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -11215,13 +11043,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>78</v>
+        <v>514</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -11239,7 +11067,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>439</v>
+        <v>515</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11254,16 +11082,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>440</v>
+        <v>517</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>441</v>
+        <v>518</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>78</v>
+        <v>519</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11271,14 +11099,12 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>520</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C77" t="s" s="2">
-        <v>497</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11299,20 +11125,18 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>261</v>
+        <v>521</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>522</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>375</v>
+        <v>523</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11336,11 +11160,13 @@
         <v>78</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>78</v>
@@ -11358,13 +11184,13 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>373</v>
+        <v>525</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
@@ -11376,13 +11202,13 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>379</v>
+        <v>108</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>380</v>
+        <v>108</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>340</v>
+        <v>78</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11390,10 +11216,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>420</v>
+        <v>526</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11413,16 +11239,16 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>105</v>
+        <v>527</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>106</v>
+        <v>528</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11473,7 +11299,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>107</v>
+        <v>529</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11485,19 +11311,19 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>108</v>
+        <v>530</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>300</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11505,14 +11331,16 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>470</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11531,18 +11359,18 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>111</v>
+        <v>533</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>112</v>
+        <v>534</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11578,19 +11406,19 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>118</v>
+        <v>470</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11599,33 +11427,33 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>119</v>
+        <v>476</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>78</v>
+        <v>478</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>108</v>
+        <v>479</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>501</v>
+        <v>536</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>536</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11639,29 +11467,27 @@
         <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>154</v>
+        <v>537</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>425</v>
+        <v>538</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>426</v>
+        <v>539</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -11685,11 +11511,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>502</v>
+        <v>78</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11707,7 +11535,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>430</v>
+        <v>536</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11725,10 +11553,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>432</v>
+        <v>541</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11739,10 +11567,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>434</v>
+        <v>542</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11762,23 +11590,19 @@
         <v>78</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>435</v>
+        <v>105</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -11826,7 +11650,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11838,16 +11662,16 @@
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>441</v>
+        <v>108</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11858,14 +11682,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>504</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11881,18 +11705,20 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>261</v>
+        <v>111</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>505</v>
+        <v>112</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -11917,11 +11743,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11939,7 +11767,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>504</v>
+        <v>118</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11951,34 +11779,34 @@
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>509</v>
+        <v>108</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>511</v>
+        <v>544</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11988,25 +11816,29 @@
         <v>80</v>
       </c>
       <c r="H83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I83" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>512</v>
+        <v>111</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>513</v>
+        <v>546</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -12054,7 +11886,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12066,7 +11898,7 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12075,21 +11907,21 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>515</v>
+        <v>199</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>516</v>
+        <v>78</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12103,7 +11935,7 @@
         <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>78</v>
@@ -12112,13 +11944,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>519</v>
+        <v>176</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12145,13 +11977,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12169,7 +12001,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12187,10 +12019,10 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>522</v>
+        <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12201,10 +12033,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12215,10 +12047,10 @@
         <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>78</v>
@@ -12227,18 +12059,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>525</v>
+        <v>325</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>526</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>527</v>
+        <v>556</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>528</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12274,41 +12104,43 @@
         <v>78</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AC85" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>530</v>
+        <v>102</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12316,10 +12148,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>535</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12342,15 +12174,17 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>104</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>105</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>560</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>561</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>78</v>
@@ -12399,7 +12233,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>107</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12411,7 +12245,7 @@
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12420,7 +12254,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>108</v>
+        <v>541</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12431,21 +12265,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>536</v>
+        <v>562</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -12457,16 +12291,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>111</v>
+        <v>558</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>112</v>
+        <v>563</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>113</v>
+        <v>564</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>114</v>
+        <v>561</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12504,31 +12338,31 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>118</v>
+        <v>562</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12537,7 +12371,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>108</v>
+        <v>541</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12546,16 +12380,14 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C88" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
@@ -12564,10 +12396,10 @@
         <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>78</v>
@@ -12576,13 +12408,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12633,7 +12465,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>118</v>
+        <v>565</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12645,7 +12477,7 @@
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12654,7 +12486,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12665,10 +12497,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>542</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12676,7 +12508,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>90</v>
@@ -12688,16 +12520,16 @@
         <v>78</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>176</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>543</v>
+        <v>105</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>544</v>
+        <v>106</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12724,13 +12556,13 @@
         <v>78</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>78</v>
@@ -12748,7 +12580,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12757,22 +12589,22 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>549</v>
+        <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>550</v>
+        <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>551</v>
+        <v>108</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>552</v>
+        <v>78</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -12780,21 +12612,21 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12803,23 +12635,21 @@
         <v>78</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>555</v>
+        <v>113</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -12867,31 +12697,31 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>558</v>
+        <v>118</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>560</v>
+        <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>561</v>
+        <v>108</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>291</v>
+        <v>78</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -12899,21 +12729,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12925,19 +12755,19 @@
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>176</v>
+        <v>111</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>565</v>
+        <v>114</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>566</v>
+        <v>228</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12962,13 +12792,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>567</v>
+        <v>78</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>568</v>
+        <v>78</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12986,31 +12816,31 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>571</v>
+        <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>572</v>
+        <v>199</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -13018,10 +12848,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13029,7 +12859,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>90</v>
@@ -13041,20 +12871,18 @@
         <v>78</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>575</v>
+        <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13103,10 +12931,10 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>90</v>
@@ -13121,7 +12949,7 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>108</v>
@@ -13135,10 +12963,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13158,16 +12986,16 @@
         <v>78</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>294</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13218,7 +13046,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13236,28 +13064,26 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>584</v>
+        <v>541</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C94" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13266,10 +13092,10 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>78</v>
@@ -13278,18 +13104,16 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>587</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>527</v>
+        <v>579</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>528</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13337,31 +13161,31 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>524</v>
+        <v>577</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>530</v>
+        <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>589</v>
+        <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13369,10 +13193,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13395,18 +13219,18 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>583</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
@@ -13454,7 +13278,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13475,1760 +13299,17 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>595</v>
+        <v>108</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO110" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO110">
+  <autoFilter ref="A1:AO95">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15238,7 +13319,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI109">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$91</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="563">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T13:37:45+00:00</t>
+    <t>2026-09-29T08:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1314,73 +1314,7 @@
     <t>Rôle fonctionnel du professionnel de santé</t>
   </si>
   <si>
-    <t>PractitionerRole.code:functionCode.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.id</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:functionCode.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.extension</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:functionCode.coding</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS|20250523120000</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code:functionCode.text</t>
-  </si>
-  <si>
-    <t>PractitionerRole.code.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>PractitionerRole.code:classCode</t>
@@ -2142,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO95"/>
+  <dimension ref="A1:AO91"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="52.48046875" customWidth="true" bestFit="true"/>
@@ -9179,11 +9113,11 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9233,12 +9167,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9256,19 +9192,23 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>105</v>
+        <v>422</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9292,13 +9232,11 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
@@ -9316,31 +9254,31 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>107</v>
+        <v>373</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>340</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9348,21 +9286,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="D62" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9371,21 +9311,23 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>112</v>
+        <v>426</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>113</v>
+        <v>375</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9409,31 +9351,29 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>78</v>
+        <v>427</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>118</v>
+        <v>373</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9445,19 +9385,19 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>78</v>
+        <v>340</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9465,10 +9405,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9491,20 +9431,16 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>261</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
       </c>
@@ -9532,7 +9468,7 @@
       </c>
       <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9550,7 +9486,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9568,24 +9504,24 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>78</v>
+        <v>434</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9596,10 +9532,10 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>78</v>
@@ -9608,20 +9544,16 @@
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>104</v>
+        <v>436</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O64" t="s" s="2">
         <v>438</v>
       </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9669,13 +9601,13 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
@@ -9687,28 +9619,26 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AN64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>78</v>
-      </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>442</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>443</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9717,32 +9647,28 @@
         <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>261</v>
+        <v>443</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>444</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9766,11 +9692,13 @@
         <v>78</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>445</v>
+        <v>78</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>78</v>
@@ -9788,7 +9716,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>373</v>
+        <v>442</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9806,13 +9734,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>379</v>
+        <v>446</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>380</v>
+        <v>447</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>340</v>
+        <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9820,14 +9748,12 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9836,31 +9762,29 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>261</v>
+        <v>449</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>377</v>
+        <v>452</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
@@ -9885,29 +9809,29 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y66" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z66" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>373</v>
+        <v>448</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9916,22 +9840,22 @@
         <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>102</v>
+        <v>454</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>78</v>
+        <v>455</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>379</v>
+        <v>456</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>457</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>340</v>
+        <v>458</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9939,10 +9863,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9953,7 +9877,7 @@
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9962,16 +9886,16 @@
         <v>78</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>261</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>451</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>452</v>
+        <v>106</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9998,11 +9922,13 @@
         <v>78</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y67" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z67" t="s" s="2">
-        <v>453</v>
+        <v>78</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>78</v>
@@ -10020,46 +9946,46 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>450</v>
+        <v>107</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>455</v>
+        <v>108</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10069,24 +9995,26 @@
         <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>458</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>459</v>
+        <v>112</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10123,19 +10051,19 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>457</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10147,7 +10075,7 @@
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10156,23 +10084,25 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="B69" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C69" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>78</v>
       </c>
@@ -10181,10 +10111,10 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>78</v>
@@ -10193,13 +10123,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10250,7 +10180,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>464</v>
+        <v>118</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10262,16 +10192,16 @@
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10282,10 +10212,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10293,33 +10223,31 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J70" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K70" t="s" s="2">
-        <v>471</v>
+        <v>176</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>474</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
@@ -10343,53 +10271,55 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="AC70" s="2"/>
-      <c r="AD70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
@@ -10397,10 +10327,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10408,7 +10338,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>90</v>
@@ -10420,19 +10350,23 @@
         <v>78</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>105</v>
+        <v>478</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>481</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -10480,7 +10414,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>107</v>
+        <v>482</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10492,19 +10426,19 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>78</v>
+        <v>484</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>108</v>
+        <v>485</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>78</v>
+        <v>291</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
@@ -10512,44 +10446,46 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>112</v>
+        <v>487</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>113</v>
+        <v>488</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10573,55 +10509,55 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>118</v>
+        <v>493</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>495</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>108</v>
+        <v>496</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>78</v>
+        <v>497</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
@@ -10629,14 +10565,12 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10654,18 +10588,20 @@
         <v>78</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>501</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>78</v>
@@ -10714,28 +10650,28 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>503</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10746,10 +10682,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10757,7 +10693,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>90</v>
@@ -10772,13 +10708,13 @@
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10805,13 +10741,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>491</v>
+        <v>78</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>492</v>
+        <v>78</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10829,7 +10765,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10838,22 +10774,22 @@
         <v>90</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>495</v>
+        <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>498</v>
+        <v>300</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -10861,21 +10797,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10884,22 +10822,20 @@
         <v>78</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>104</v>
+        <v>511</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -10948,42 +10884,42 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>504</v>
+        <v>448</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>102</v>
+        <v>454</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>291</v>
+        <v>458</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10994,32 +10930,30 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>176</v>
+        <v>515</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11043,37 +10977,37 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="AA76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>515</v>
-      </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
@@ -11082,16 +11016,16 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>516</v>
+        <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11122,20 +11056,18 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>521</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>524</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
@@ -11184,7 +11116,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>525</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11196,13 +11128,13 @@
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>108</v>
@@ -11216,21 +11148,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11239,18 +11171,20 @@
         <v>78</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>527</v>
+        <v>112</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11299,31 +11233,31 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>529</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11331,16 +11265,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11353,23 +11285,25 @@
         <v>78</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>533</v>
+        <v>111</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O79" t="s" s="2">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11418,7 +11352,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11427,33 +11361,33 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>476</v>
+        <v>119</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>479</v>
+        <v>199</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>480</v>
+        <v>78</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11467,7 +11401,7 @@
         <v>80</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>78</v>
@@ -11476,17 +11410,15 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>537</v>
+        <v>176</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -11511,13 +11443,13 @@
         <v>78</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11535,7 +11467,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11556,7 +11488,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11567,10 +11499,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11593,13 +11525,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>325</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>105</v>
+        <v>533</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>106</v>
+        <v>534</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11650,7 +11582,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>107</v>
+        <v>532</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11662,7 +11594,7 @@
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11671,7 +11603,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11682,21 +11614,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
@@ -11708,16 +11640,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>111</v>
+        <v>536</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>112</v>
+        <v>537</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>113</v>
+        <v>538</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>114</v>
+        <v>539</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11767,19 +11699,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>118</v>
+        <v>535</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11788,7 +11720,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11799,46 +11731,44 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>111</v>
+        <v>536</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
@@ -11886,19 +11816,19 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -11907,7 +11837,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>199</v>
+        <v>519</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -11916,12 +11846,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11935,7 +11865,7 @@
         <v>80</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>78</v>
@@ -11944,13 +11874,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>176</v>
+        <v>515</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -11977,13 +11907,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>552</v>
+        <v>78</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>553</v>
+        <v>78</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -12001,7 +11931,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12022,7 +11952,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12033,10 +11963,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12059,13 +11989,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>555</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>556</v>
+        <v>106</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12116,7 +12046,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>554</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12128,7 +12058,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12137,7 +12067,7 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>541</v>
+        <v>108</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12148,21 +12078,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12174,16 +12104,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>558</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>559</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>560</v>
+        <v>113</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>561</v>
+        <v>114</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12233,19 +12163,19 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>557</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12254,7 +12184,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>541</v>
+        <v>108</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12265,44 +12195,46 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>558</v>
+        <v>111</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>563</v>
+        <v>524</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>564</v>
+        <v>525</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12350,19 +12282,19 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>562</v>
+        <v>526</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12371,7 +12303,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>541</v>
+        <v>199</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12380,12 +12312,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12393,13 +12325,13 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>78</v>
@@ -12408,13 +12340,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>537</v>
+        <v>104</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12465,13 +12397,13 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>565</v>
+        <v>549</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
@@ -12486,7 +12418,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>541</v>
+        <v>108</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12497,10 +12429,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12523,13 +12455,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>104</v>
+        <v>294</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>105</v>
+        <v>553</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>106</v>
+        <v>554</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12580,7 +12512,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>107</v>
+        <v>552</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12592,7 +12524,7 @@
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12601,7 +12533,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12610,26 +12542,26 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>78</v>
@@ -12638,17 +12570,15 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>112</v>
+        <v>556</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
@@ -12697,19 +12627,19 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>118</v>
+        <v>555</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -12718,7 +12648,7 @@
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>108</v>
+        <v>519</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12727,16 +12657,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>545</v>
+        <v>78</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12746,28 +12676,26 @@
         <v>80</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>111</v>
+        <v>559</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>228</v>
+        <v>562</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -12816,7 +12744,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>548</v>
+        <v>558</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12828,7 +12756,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12837,479 +12765,17 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>199</v>
+        <v>108</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="L93" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO95" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO95">
+  <autoFilter ref="A1:AO91">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13319,7 +12785,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI90">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T08:08:01+00:00</t>
+    <t>2026-09-29T09:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
+++ b/correctionProfile/ig/StructureDefinition-fr-practitionerRole-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T09:01:26+00:00</t>
+    <t>2026-09-30T14:16:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -490,7 +490,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner-role|2.2.0</t>
   </si>
   <si>
     <t>PractitionerRole.meta.security</t>
@@ -658,7 +658,7 @@
     <t>serviceTypeDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-service-type-duration|2.2.0}
 </t>
   </si>
   <si>
@@ -1191,7 +1191,7 @@
     <t>Need to know what authority the practitioner has - what can they do?</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-role-exercice|2.2.0</t>
   </si>
   <si>
     <t>PRD-1 / STF-18  / PRA-3  / PRT-4  / ROL-3 / ORC-12 / OBR-16 / PV1-7 / PV1-8 / PV1-9 / PV1-17</t>
@@ -1350,7 +1350,7 @@
     <t>Specific specialty of the practitioner.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-practitioner-specialty|2.2.0</t>
   </si>
   <si>
     <t>PRA-5</t>
@@ -1365,7 +1365,7 @@
     <t>PractitionerRole.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-location|2.2.0)
 </t>
   </si>
   <si>
@@ -1387,7 +1387,7 @@
     <t>PractitionerRole.healthcareService</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-healthcare-service|2.2.0)
 </t>
   </si>
   <si>
@@ -1406,7 +1406,7 @@
     <t>PractitionerRole.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1451,7 +1451,7 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
